--- a/tts_envs/data/shops.xlsx
+++ b/tts_envs/data/shops.xlsx
@@ -445,12 +445,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.140625" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="2">
@@ -472,6 +473,11 @@
       <c r="D1" s="5" t="inlineStr">
         <is>
           <t>adjustment_sell</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>contraband_buyer</t>
         </is>
       </c>
     </row>
